--- a/ROSA_vitaSPEC/Results/test_pretraitements/trans.beta.carotenes/Resultats_trans.beta.carotenes_moy_R2.xlsx
+++ b/ROSA_vitaSPEC/Results/test_pretraitements/trans.beta.carotenes/Resultats_trans.beta.carotenes_moy_R2.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P47"/>
+  <dimension ref="A1:Q43"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -362,75 +362,80 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>LV0_R2</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
           <t>LV1_R2</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>LV2_R2</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>LV3_R2</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>LV4_R2</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>LV5_R2</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>LV6_R2</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>LV7_R2</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>LV8_R2</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>LV9_R2</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>LV10_R2</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>LV11_R2</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>LV12_R2</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>LV13_R2</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>LV14_R2</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>LV15_R2</t>
         </is>
@@ -443,48 +448,51 @@
         </is>
       </c>
       <c r="B2">
+        <v>0</v>
+      </c>
+      <c r="C2">
         <v>0.3752567795432458</v>
       </c>
-      <c r="C2">
+      <c r="D2">
         <v>0.5416653528505193</v>
       </c>
-      <c r="D2">
+      <c r="E2">
         <v>0.5895828684761761</v>
       </c>
-      <c r="E2">
+      <c r="F2">
         <v>0.6158127165065681</v>
       </c>
-      <c r="F2">
+      <c r="G2">
         <v>0.6484331903262435</v>
       </c>
-      <c r="G2">
+      <c r="H2">
         <v>0.6683285505560765</v>
       </c>
-      <c r="H2">
+      <c r="I2">
         <v>0.6904675806373614</v>
       </c>
-      <c r="I2">
+      <c r="J2">
         <v>0.6984609181145375</v>
       </c>
-      <c r="J2">
+      <c r="K2">
         <v>0.716328715721119</v>
       </c>
-      <c r="K2">
+      <c r="L2">
         <v>0.7256655460126531</v>
       </c>
-      <c r="L2">
+      <c r="M2">
         <v>0.751990997604761</v>
       </c>
-      <c r="M2">
+      <c r="N2">
         <v>0.7684406075582383</v>
       </c>
-      <c r="N2">
+      <c r="O2">
         <v>0.8018741945830847</v>
       </c>
-      <c r="O2">
+      <c r="P2">
         <v>0.8423913285336595</v>
       </c>
-      <c r="P2">
+      <c r="Q2">
         <v>0.8568615165202507</v>
       </c>
     </row>
@@ -495,48 +503,51 @@
         </is>
       </c>
       <c r="B3">
+        <v>0</v>
+      </c>
+      <c r="C3">
         <v>0.4793798187760882</v>
       </c>
-      <c r="C3">
+      <c r="D3">
         <v>0.5391636159352458</v>
       </c>
-      <c r="D3">
+      <c r="E3">
         <v>0.5779701650527165</v>
       </c>
-      <c r="E3">
+      <c r="F3">
         <v>0.6174601666853482</v>
       </c>
-      <c r="F3">
+      <c r="G3">
         <v>0.6557193287202603</v>
       </c>
-      <c r="G3">
+      <c r="H3">
         <v>0.6908295780283253</v>
       </c>
-      <c r="H3">
+      <c r="I3">
         <v>0.7148184433345254</v>
       </c>
-      <c r="I3">
+      <c r="J3">
         <v>0.7389291361450663</v>
       </c>
-      <c r="J3">
+      <c r="K3">
         <v>0.7493907197223999</v>
       </c>
-      <c r="K3">
+      <c r="L3">
         <v>0.766169244140446</v>
       </c>
-      <c r="L3">
+      <c r="M3">
         <v>0.7840836205510882</v>
       </c>
-      <c r="M3">
+      <c r="N3">
         <v>0.8041487257113942</v>
       </c>
-      <c r="N3">
+      <c r="O3">
         <v>0.8322863331751957</v>
       </c>
-      <c r="O3">
+      <c r="P3">
         <v>0.8453317889951585</v>
       </c>
-      <c r="P3">
+      <c r="Q3">
         <v>0.8621304620468452</v>
       </c>
     </row>
@@ -547,48 +558,51 @@
         </is>
       </c>
       <c r="B4">
+        <v>0</v>
+      </c>
+      <c r="C4">
         <v>0.389992437131612</v>
       </c>
-      <c r="C4">
+      <c r="D4">
         <v>0.5242149813676271</v>
       </c>
-      <c r="D4">
+      <c r="E4">
         <v>0.5512004301429156</v>
       </c>
-      <c r="E4">
+      <c r="F4">
         <v>0.5900937841962893</v>
       </c>
-      <c r="F4">
+      <c r="G4">
         <v>0.6534360461656892</v>
       </c>
-      <c r="G4">
+      <c r="H4">
         <v>0.67215686531901</v>
       </c>
-      <c r="H4">
+      <c r="I4">
         <v>0.6896849290628085</v>
       </c>
-      <c r="I4">
+      <c r="J4">
         <v>0.6979998391105267</v>
       </c>
-      <c r="J4">
+      <c r="K4">
         <v>0.7229538829970301</v>
       </c>
-      <c r="K4">
+      <c r="L4">
         <v>0.7588320221578243</v>
       </c>
-      <c r="L4">
+      <c r="M4">
         <v>0.801455177809006</v>
       </c>
-      <c r="M4">
+      <c r="N4">
         <v>0.8151677638008773</v>
       </c>
-      <c r="N4">
+      <c r="O4">
         <v>0.8430257032340192</v>
       </c>
-      <c r="O4">
+      <c r="P4">
         <v>0.8525189245083138</v>
       </c>
-      <c r="P4">
+      <c r="Q4">
         <v>0.8621190942054902</v>
       </c>
     </row>
@@ -599,48 +613,51 @@
         </is>
       </c>
       <c r="B5">
+        <v>0</v>
+      </c>
+      <c r="C5">
         <v>0.5191279020097238</v>
       </c>
-      <c r="C5">
+      <c r="D5">
         <v>0.5499866445366832</v>
       </c>
-      <c r="D5">
+      <c r="E5">
         <v>0.609995087816777</v>
       </c>
-      <c r="E5">
+      <c r="F5">
         <v>0.6503018045855855</v>
       </c>
-      <c r="F5">
+      <c r="G5">
         <v>0.6834380940827083</v>
       </c>
-      <c r="G5">
+      <c r="H5">
         <v>0.693629799528495</v>
       </c>
-      <c r="H5">
+      <c r="I5">
         <v>0.7118814669490663</v>
       </c>
-      <c r="I5">
+      <c r="J5">
         <v>0.7247450976155818</v>
       </c>
-      <c r="J5">
+      <c r="K5">
         <v>0.7481429067496763</v>
       </c>
-      <c r="K5">
+      <c r="L5">
         <v>0.769191775822056</v>
       </c>
-      <c r="L5">
+      <c r="M5">
         <v>0.7978344952633206</v>
       </c>
-      <c r="M5">
+      <c r="N5">
         <v>0.8315409248573035</v>
       </c>
-      <c r="N5">
+      <c r="O5">
         <v>0.8532733446820632</v>
       </c>
-      <c r="O5">
+      <c r="P5">
         <v>0.8751453015771137</v>
       </c>
-      <c r="P5">
+      <c r="Q5">
         <v>0.8886816065091649</v>
       </c>
     </row>
@@ -651,48 +668,51 @@
         </is>
       </c>
       <c r="B6">
+        <v>0</v>
+      </c>
+      <c r="C6">
         <v>0.5202960581277887</v>
       </c>
-      <c r="C6">
+      <c r="D6">
         <v>0.5481004731159367</v>
       </c>
-      <c r="D6">
+      <c r="E6">
         <v>0.591809913392758</v>
       </c>
-      <c r="E6">
+      <c r="F6">
         <v>0.6281181115578106</v>
       </c>
-      <c r="F6">
+      <c r="G6">
         <v>0.6834766517042058</v>
       </c>
-      <c r="G6">
+      <c r="H6">
         <v>0.6945882905011165</v>
       </c>
-      <c r="H6">
+      <c r="I6">
         <v>0.703877022308889</v>
       </c>
-      <c r="I6">
+      <c r="J6">
         <v>0.7211214928284192</v>
       </c>
-      <c r="J6">
+      <c r="K6">
         <v>0.7417266945754379</v>
       </c>
-      <c r="K6">
+      <c r="L6">
         <v>0.7537095006458187</v>
       </c>
-      <c r="L6">
+      <c r="M6">
         <v>0.7849866273266688</v>
       </c>
-      <c r="M6">
+      <c r="N6">
         <v>0.8094478938038474</v>
       </c>
-      <c r="N6">
+      <c r="O6">
         <v>0.8457870379707442</v>
       </c>
-      <c r="O6">
+      <c r="P6">
         <v>0.8566590465821503</v>
       </c>
-      <c r="P6">
+      <c r="Q6">
         <v>0.8626390272891264</v>
       </c>
     </row>
@@ -703,48 +723,51 @@
         </is>
       </c>
       <c r="B7">
+        <v>0</v>
+      </c>
+      <c r="C7">
         <v>0.3890730185094939</v>
       </c>
-      <c r="C7">
+      <c r="D7">
         <v>0.5361228372658106</v>
       </c>
-      <c r="D7">
+      <c r="E7">
         <v>0.6250319079338261</v>
       </c>
-      <c r="E7">
+      <c r="F7">
         <v>0.6479749992635673</v>
       </c>
-      <c r="F7">
+      <c r="G7">
         <v>0.6768621436519598</v>
       </c>
-      <c r="G7">
+      <c r="H7">
         <v>0.6861423105291907</v>
       </c>
-      <c r="H7">
+      <c r="I7">
         <v>0.705699537984203</v>
       </c>
-      <c r="I7">
+      <c r="J7">
         <v>0.7198330737525522</v>
       </c>
-      <c r="J7">
+      <c r="K7">
         <v>0.7259551110766249</v>
       </c>
-      <c r="K7">
+      <c r="L7">
         <v>0.752016031902523</v>
       </c>
-      <c r="L7">
+      <c r="M7">
         <v>0.7822158850436578</v>
       </c>
-      <c r="M7">
+      <c r="N7">
         <v>0.8112617730430708</v>
       </c>
-      <c r="N7">
+      <c r="O7">
         <v>0.827775500371936</v>
       </c>
-      <c r="O7">
+      <c r="P7">
         <v>0.8484519693458564</v>
       </c>
-      <c r="P7">
+      <c r="Q7">
         <v>0.8585808599962608</v>
       </c>
     </row>
@@ -755,48 +778,51 @@
         </is>
       </c>
       <c r="B8">
+        <v>0</v>
+      </c>
+      <c r="C8">
         <v>0.4359814469112047</v>
       </c>
-      <c r="C8">
+      <c r="D8">
         <v>0.5167237355933945</v>
       </c>
-      <c r="D8">
+      <c r="E8">
         <v>0.5949340534795116</v>
       </c>
-      <c r="E8">
+      <c r="F8">
         <v>0.6270500307550413</v>
       </c>
-      <c r="F8">
+      <c r="G8">
         <v>0.6406656453585138</v>
       </c>
-      <c r="G8">
+      <c r="H8">
         <v>0.6856681245543574</v>
       </c>
-      <c r="H8">
+      <c r="I8">
         <v>0.6979312031228148</v>
       </c>
-      <c r="I8">
+      <c r="J8">
         <v>0.7113149049011422</v>
       </c>
-      <c r="J8">
+      <c r="K8">
         <v>0.7273808281698759</v>
       </c>
-      <c r="K8">
+      <c r="L8">
         <v>0.7529038467361218</v>
       </c>
-      <c r="L8">
+      <c r="M8">
         <v>0.7927955662597848</v>
       </c>
-      <c r="M8">
+      <c r="N8">
         <v>0.8081364233948848</v>
       </c>
-      <c r="N8">
+      <c r="O8">
         <v>0.8290579375180426</v>
       </c>
-      <c r="O8">
+      <c r="P8">
         <v>0.8397278785139126</v>
       </c>
-      <c r="P8">
+      <c r="Q8">
         <v>0.8503653685952723</v>
       </c>
     </row>
@@ -807,48 +833,51 @@
         </is>
       </c>
       <c r="B9">
+        <v>0</v>
+      </c>
+      <c r="C9">
         <v>0.4359481655459926</v>
       </c>
-      <c r="C9">
+      <c r="D9">
         <v>0.5166685187359685</v>
       </c>
-      <c r="D9">
+      <c r="E9">
         <v>0.5941588745432154</v>
       </c>
-      <c r="E9">
+      <c r="F9">
         <v>0.6243604146582444</v>
       </c>
-      <c r="F9">
+      <c r="G9">
         <v>0.6364007057468952</v>
       </c>
-      <c r="G9">
+      <c r="H9">
         <v>0.6759656841436904</v>
       </c>
-      <c r="H9">
+      <c r="I9">
         <v>0.6865623483330268</v>
       </c>
-      <c r="I9">
+      <c r="J9">
         <v>0.6965002541155192</v>
       </c>
-      <c r="J9">
+      <c r="K9">
         <v>0.7040285036072036</v>
       </c>
-      <c r="K9">
+      <c r="L9">
         <v>0.714763314158826</v>
       </c>
-      <c r="L9">
+      <c r="M9">
         <v>0.7418936727383384</v>
       </c>
-      <c r="M9">
+      <c r="N9">
         <v>0.75569774922354</v>
       </c>
-      <c r="N9">
+      <c r="O9">
         <v>0.766037773642113</v>
       </c>
-      <c r="O9">
+      <c r="P9">
         <v>0.781925686588604</v>
       </c>
-      <c r="P9">
+      <c r="Q9">
         <v>0.7870910911172468</v>
       </c>
     </row>
@@ -859,48 +888,51 @@
         </is>
       </c>
       <c r="B10">
+        <v>0</v>
+      </c>
+      <c r="C10">
         <v>0.4359134091771651</v>
       </c>
-      <c r="C10">
+      <c r="D10">
         <v>0.5166593407320008</v>
       </c>
-      <c r="D10">
+      <c r="E10">
         <v>0.5941515282214567</v>
       </c>
-      <c r="E10">
+      <c r="F10">
         <v>0.6243316093873357</v>
       </c>
-      <c r="F10">
+      <c r="G10">
         <v>0.6363192741019721</v>
       </c>
-      <c r="G10">
+      <c r="H10">
         <v>0.6755985062927969</v>
       </c>
-      <c r="H10">
+      <c r="I10">
         <v>0.6862030867870736</v>
       </c>
-      <c r="I10">
+      <c r="J10">
         <v>0.6961100291617104</v>
       </c>
-      <c r="J10">
+      <c r="K10">
         <v>0.7035190828363311</v>
       </c>
-      <c r="K10">
+      <c r="L10">
         <v>0.7137922068939876</v>
       </c>
-      <c r="L10">
+      <c r="M10">
         <v>0.7411179766053184</v>
       </c>
-      <c r="M10">
+      <c r="N10">
         <v>0.7537471050776069</v>
       </c>
-      <c r="N10">
+      <c r="O10">
         <v>0.7620124495721563</v>
       </c>
-      <c r="O10">
+      <c r="P10">
         <v>0.7762674896820153</v>
       </c>
-      <c r="P10">
+      <c r="Q10">
         <v>0.7806078586468083</v>
       </c>
     </row>
@@ -911,48 +943,51 @@
         </is>
       </c>
       <c r="B11">
+        <v>0</v>
+      </c>
+      <c r="C11">
         <v>0.4359482530299308</v>
       </c>
-      <c r="C11">
+      <c r="D11">
         <v>0.5166598724090934</v>
       </c>
-      <c r="D11">
+      <c r="E11">
         <v>0.5942323774558083</v>
       </c>
-      <c r="E11">
+      <c r="F11">
         <v>0.6245601099879646</v>
       </c>
-      <c r="F11">
+      <c r="G11">
         <v>0.6366844361346176</v>
       </c>
-      <c r="G11">
+      <c r="H11">
         <v>0.6768867314618856</v>
       </c>
-      <c r="H11">
+      <c r="I11">
         <v>0.6870087901430441</v>
       </c>
-      <c r="I11">
+      <c r="J11">
         <v>0.6970766300397273</v>
       </c>
-      <c r="J11">
+      <c r="K11">
         <v>0.7046985506295474</v>
       </c>
-      <c r="K11">
+      <c r="L11">
         <v>0.7152050464166742</v>
       </c>
-      <c r="L11">
+      <c r="M11">
         <v>0.7408211417846844</v>
       </c>
-      <c r="M11">
+      <c r="N11">
         <v>0.7569240738609204</v>
       </c>
-      <c r="N11">
+      <c r="O11">
         <v>0.7678828487548202</v>
       </c>
-      <c r="O11">
+      <c r="P11">
         <v>0.7803961806355304</v>
       </c>
-      <c r="P11">
+      <c r="Q11">
         <v>0.7884046054417886</v>
       </c>
     </row>
@@ -963,48 +998,51 @@
         </is>
       </c>
       <c r="B12">
+        <v>0</v>
+      </c>
+      <c r="C12">
         <v>0.5271888073407753</v>
       </c>
-      <c r="C12">
+      <c r="D12">
         <v>0.5622766103067092</v>
       </c>
-      <c r="D12">
+      <c r="E12">
         <v>0.639429198185443</v>
       </c>
-      <c r="E12">
+      <c r="F12">
         <v>0.6645780032006586</v>
       </c>
-      <c r="F12">
+      <c r="G12">
         <v>0.6933782976046712</v>
       </c>
-      <c r="G12">
+      <c r="H12">
         <v>0.7130605467844697</v>
       </c>
-      <c r="H12">
+      <c r="I12">
         <v>0.7272936705795534</v>
       </c>
-      <c r="I12">
+      <c r="J12">
         <v>0.7392351198453584</v>
       </c>
-      <c r="J12">
+      <c r="K12">
         <v>0.7546709845848427</v>
       </c>
-      <c r="K12">
+      <c r="L12">
         <v>0.7752895122595324</v>
       </c>
-      <c r="L12">
+      <c r="M12">
         <v>0.7965893667519733</v>
       </c>
-      <c r="M12">
+      <c r="N12">
         <v>0.8239466242605986</v>
       </c>
-      <c r="N12">
+      <c r="O12">
         <v>0.8336670885242072</v>
       </c>
-      <c r="O12">
+      <c r="P12">
         <v>0.8547449673013422</v>
       </c>
-      <c r="P12">
+      <c r="Q12">
         <v>0.8685391280933327</v>
       </c>
     </row>
@@ -1015,48 +1053,51 @@
         </is>
       </c>
       <c r="B13">
+        <v>0</v>
+      </c>
+      <c r="C13">
         <v>0.5278645048226954</v>
       </c>
-      <c r="C13">
+      <c r="D13">
         <v>0.5735485956970565</v>
       </c>
-      <c r="D13">
+      <c r="E13">
         <v>0.6322756157203361</v>
       </c>
-      <c r="E13">
+      <c r="F13">
         <v>0.6561972785157828</v>
       </c>
-      <c r="F13">
+      <c r="G13">
         <v>0.6899579747213141</v>
       </c>
-      <c r="G13">
+      <c r="H13">
         <v>0.7161923397859533</v>
       </c>
-      <c r="H13">
+      <c r="I13">
         <v>0.7368616661208716</v>
       </c>
-      <c r="I13">
+      <c r="J13">
         <v>0.7572114294819264</v>
       </c>
-      <c r="J13">
+      <c r="K13">
         <v>0.7747600937728042</v>
       </c>
-      <c r="K13">
+      <c r="L13">
         <v>0.7941246226466949</v>
       </c>
-      <c r="L13">
+      <c r="M13">
         <v>0.8040482257766468</v>
       </c>
-      <c r="M13">
+      <c r="N13">
         <v>0.8125651776939571</v>
       </c>
-      <c r="N13">
+      <c r="O13">
         <v>0.8247161585287671</v>
       </c>
-      <c r="O13">
+      <c r="P13">
         <v>0.8368207382906041</v>
       </c>
-      <c r="P13">
+      <c r="Q13">
         <v>0.8479974960779545</v>
       </c>
     </row>
@@ -1067,48 +1108,51 @@
         </is>
       </c>
       <c r="B14">
+        <v>0</v>
+      </c>
+      <c r="C14">
         <v>0.3890654636894454</v>
       </c>
-      <c r="C14">
+      <c r="D14">
         <v>0.5360787555901134</v>
       </c>
-      <c r="D14">
+      <c r="E14">
         <v>0.6248095142462365</v>
       </c>
-      <c r="E14">
+      <c r="F14">
         <v>0.6475590912170615</v>
       </c>
-      <c r="F14">
+      <c r="G14">
         <v>0.6756276990987218</v>
       </c>
-      <c r="G14">
+      <c r="H14">
         <v>0.6842720627770925</v>
       </c>
-      <c r="H14">
+      <c r="I14">
         <v>0.702068758603299</v>
       </c>
-      <c r="I14">
+      <c r="J14">
         <v>0.7123888600727888</v>
       </c>
-      <c r="J14">
+      <c r="K14">
         <v>0.7158187377858632</v>
       </c>
-      <c r="K14">
+      <c r="L14">
         <v>0.7319294661731843</v>
       </c>
-      <c r="L14">
+      <c r="M14">
         <v>0.7462237918272039</v>
       </c>
-      <c r="M14">
+      <c r="N14">
         <v>0.770258134291507</v>
       </c>
-      <c r="N14">
+      <c r="O14">
         <v>0.7822060780959736</v>
       </c>
-      <c r="O14">
+      <c r="P14">
         <v>0.7949772054450512</v>
       </c>
-      <c r="P14">
+      <c r="Q14">
         <v>0.8032137741793979</v>
       </c>
     </row>
@@ -1119,48 +1163,51 @@
         </is>
       </c>
       <c r="B15">
+        <v>0</v>
+      </c>
+      <c r="C15">
         <v>0.3890430125002379</v>
       </c>
-      <c r="C15">
+      <c r="D15">
         <v>0.536090157474054</v>
       </c>
-      <c r="D15">
+      <c r="E15">
         <v>0.6247978399639388</v>
       </c>
-      <c r="E15">
+      <c r="F15">
         <v>0.6475142605576674</v>
       </c>
-      <c r="F15">
+      <c r="G15">
         <v>0.675279406276023</v>
       </c>
-      <c r="G15">
+      <c r="H15">
         <v>0.6836815306483319</v>
       </c>
-      <c r="H15">
+      <c r="I15">
         <v>0.7009722652482577</v>
       </c>
-      <c r="I15">
+      <c r="J15">
         <v>0.7105961007194168</v>
       </c>
-      <c r="J15">
+      <c r="K15">
         <v>0.713746865993526</v>
       </c>
-      <c r="K15">
+      <c r="L15">
         <v>0.728345017338152</v>
       </c>
-      <c r="L15">
+      <c r="M15">
         <v>0.7407813989706666</v>
       </c>
-      <c r="M15">
+      <c r="N15">
         <v>0.7632518885077033</v>
       </c>
-      <c r="N15">
+      <c r="O15">
         <v>0.7753719318978728</v>
       </c>
-      <c r="O15">
+      <c r="P15">
         <v>0.7881211004861566</v>
       </c>
-      <c r="P15">
+      <c r="Q15">
         <v>0.7969249193815287</v>
       </c>
     </row>
@@ -1171,48 +1218,51 @@
         </is>
       </c>
       <c r="B16">
+        <v>0</v>
+      </c>
+      <c r="C16">
         <v>0.3890145721515335</v>
       </c>
-      <c r="C16">
+      <c r="D16">
         <v>0.5361027461893669</v>
       </c>
-      <c r="D16">
+      <c r="E16">
         <v>0.624787548602822</v>
       </c>
-      <c r="E16">
+      <c r="F16">
         <v>0.6474882431826559</v>
       </c>
-      <c r="F16">
+      <c r="G16">
         <v>0.6751547783442113</v>
       </c>
-      <c r="G16">
+      <c r="H16">
         <v>0.6834867606461867</v>
       </c>
-      <c r="H16">
+      <c r="I16">
         <v>0.7006624792584619</v>
       </c>
-      <c r="I16">
+      <c r="J16">
         <v>0.7104194538913451</v>
       </c>
-      <c r="J16">
+      <c r="K16">
         <v>0.7134821325996779</v>
       </c>
-      <c r="K16">
+      <c r="L16">
         <v>0.7276856179921338</v>
       </c>
-      <c r="L16">
+      <c r="M16">
         <v>0.7391080622373443</v>
       </c>
-      <c r="M16">
+      <c r="N16">
         <v>0.7605752997476972</v>
       </c>
-      <c r="N16">
+      <c r="O16">
         <v>0.7719045080224154</v>
       </c>
-      <c r="O16">
+      <c r="P16">
         <v>0.7838272594350597</v>
       </c>
-      <c r="P16">
+      <c r="Q16">
         <v>0.7921300653641091</v>
       </c>
     </row>
@@ -1223,48 +1273,51 @@
         </is>
       </c>
       <c r="B17">
+        <v>0</v>
+      </c>
+      <c r="C17">
         <v>0.3889423988772449</v>
       </c>
-      <c r="C17">
+      <c r="D17">
         <v>0.5361094319611094</v>
       </c>
-      <c r="D17">
+      <c r="E17">
         <v>0.6247294613198822</v>
       </c>
-      <c r="E17">
+      <c r="F17">
         <v>0.6474143579938911</v>
       </c>
-      <c r="F17">
+      <c r="G17">
         <v>0.6748846733118342</v>
       </c>
-      <c r="G17">
+      <c r="H17">
         <v>0.683105145305809</v>
       </c>
-      <c r="H17">
+      <c r="I17">
         <v>0.7000913228108768</v>
       </c>
-      <c r="I17">
+      <c r="J17">
         <v>0.7102544639103323</v>
       </c>
-      <c r="J17">
+      <c r="K17">
         <v>0.7134083284655659</v>
       </c>
-      <c r="K17">
+      <c r="L17">
         <v>0.7276698740849217</v>
       </c>
-      <c r="L17">
+      <c r="M17">
         <v>0.7387617469620303</v>
       </c>
-      <c r="M17">
+      <c r="N17">
         <v>0.7603410774874197</v>
       </c>
-      <c r="N17">
+      <c r="O17">
         <v>0.7711201845112475</v>
       </c>
-      <c r="O17">
+      <c r="P17">
         <v>0.7832887524332526</v>
       </c>
-      <c r="P17">
+      <c r="Q17">
         <v>0.7919004961626513</v>
       </c>
     </row>
@@ -1275,48 +1328,51 @@
         </is>
       </c>
       <c r="B18">
+        <v>0</v>
+      </c>
+      <c r="C18">
         <v>0.5295721605868542</v>
       </c>
-      <c r="C18">
+      <c r="D18">
         <v>0.5657064469808548</v>
       </c>
-      <c r="D18">
+      <c r="E18">
         <v>0.6367231433485316</v>
       </c>
-      <c r="E18">
+      <c r="F18">
         <v>0.6707067269197731</v>
       </c>
-      <c r="F18">
+      <c r="G18">
         <v>0.7020970095118734</v>
       </c>
-      <c r="G18">
+      <c r="H18">
         <v>0.7210840595563726</v>
       </c>
-      <c r="H18">
+      <c r="I18">
         <v>0.7293327199956976</v>
       </c>
-      <c r="I18">
+      <c r="J18">
         <v>0.7482568623447838</v>
       </c>
-      <c r="J18">
+      <c r="K18">
         <v>0.7675437790220955</v>
       </c>
-      <c r="K18">
+      <c r="L18">
         <v>0.7850601824985957</v>
       </c>
-      <c r="L18">
+      <c r="M18">
         <v>0.81043950074684</v>
       </c>
-      <c r="M18">
+      <c r="N18">
         <v>0.8430808055773465</v>
       </c>
-      <c r="N18">
+      <c r="O18">
         <v>0.8558336262414719</v>
       </c>
-      <c r="O18">
+      <c r="P18">
         <v>0.874477440199624</v>
       </c>
-      <c r="P18">
+      <c r="Q18">
         <v>0.8921560049304859</v>
       </c>
     </row>
@@ -1327,48 +1383,51 @@
         </is>
       </c>
       <c r="B19">
+        <v>0</v>
+      </c>
+      <c r="C19">
         <v>0.5309841238634667</v>
       </c>
-      <c r="C19">
+      <c r="D19">
         <v>0.5636343841738536</v>
       </c>
-      <c r="D19">
+      <c r="E19">
         <v>0.6121533697505517</v>
       </c>
-      <c r="E19">
+      <c r="F19">
         <v>0.6492203153622629</v>
       </c>
-      <c r="F19">
+      <c r="G19">
         <v>0.6937107242351579</v>
       </c>
-      <c r="G19">
+      <c r="H19">
         <v>0.7030439005503426</v>
       </c>
-      <c r="H19">
+      <c r="I19">
         <v>0.7124673346274417</v>
       </c>
-      <c r="I19">
+      <c r="J19">
         <v>0.7289410773870177</v>
       </c>
-      <c r="J19">
+      <c r="K19">
         <v>0.7482173470737623</v>
       </c>
-      <c r="K19">
+      <c r="L19">
         <v>0.7720068217735845</v>
       </c>
-      <c r="L19">
+      <c r="M19">
         <v>0.800860728506079</v>
       </c>
-      <c r="M19">
+      <c r="N19">
         <v>0.8153572099346699</v>
       </c>
-      <c r="N19">
+      <c r="O19">
         <v>0.8362419654892592</v>
       </c>
-      <c r="O19">
+      <c r="P19">
         <v>0.8469689414191809</v>
       </c>
-      <c r="P19">
+      <c r="Q19">
         <v>0.8601230206502362</v>
       </c>
     </row>
@@ -1379,48 +1438,51 @@
         </is>
       </c>
       <c r="B20">
+        <v>0</v>
+      </c>
+      <c r="C20">
         <v>0.5311769532725055</v>
       </c>
-      <c r="C20">
+      <c r="D20">
         <v>0.5639212440999821</v>
       </c>
-      <c r="D20">
+      <c r="E20">
         <v>0.6175474398311149</v>
       </c>
-      <c r="E20">
+      <c r="F20">
         <v>0.6768322237087272</v>
       </c>
-      <c r="F20">
+      <c r="G20">
         <v>0.6891206827367884</v>
       </c>
-      <c r="G20">
+      <c r="H20">
         <v>0.7012387936623966</v>
       </c>
-      <c r="H20">
+      <c r="I20">
         <v>0.7068204375910326</v>
       </c>
-      <c r="I20">
+      <c r="J20">
         <v>0.7183493148123726</v>
       </c>
-      <c r="J20">
+      <c r="K20">
         <v>0.7351908488875436</v>
       </c>
-      <c r="K20">
+      <c r="L20">
         <v>0.7590346217926115</v>
       </c>
-      <c r="L20">
+      <c r="M20">
         <v>0.7871773987219245</v>
       </c>
-      <c r="M20">
+      <c r="N20">
         <v>0.8102804052455506</v>
       </c>
-      <c r="N20">
+      <c r="O20">
         <v>0.8249128805188273</v>
       </c>
-      <c r="O20">
+      <c r="P20">
         <v>0.8404351060800686</v>
       </c>
-      <c r="P20">
+      <c r="Q20">
         <v>0.8574824988957133</v>
       </c>
     </row>
@@ -1431,48 +1493,51 @@
         </is>
       </c>
       <c r="B21">
+        <v>0</v>
+      </c>
+      <c r="C21">
         <v>0.4779097286492605</v>
       </c>
-      <c r="C21">
+      <c r="D21">
         <v>0.5363512147805647</v>
       </c>
-      <c r="D21">
+      <c r="E21">
         <v>0.5742691401258102</v>
       </c>
-      <c r="E21">
+      <c r="F21">
         <v>0.6202994150971448</v>
       </c>
-      <c r="F21">
+      <c r="G21">
         <v>0.6688126786862411</v>
       </c>
-      <c r="G21">
+      <c r="H21">
         <v>0.7038027742814768</v>
       </c>
-      <c r="H21">
+      <c r="I21">
         <v>0.7203600271839763</v>
       </c>
-      <c r="I21">
+      <c r="J21">
         <v>0.7464411152843885</v>
       </c>
-      <c r="J21">
+      <c r="K21">
         <v>0.7719266575981447</v>
       </c>
-      <c r="K21">
+      <c r="L21">
         <v>0.7861248698063497</v>
       </c>
-      <c r="L21">
+      <c r="M21">
         <v>0.7976563177130338</v>
       </c>
-      <c r="M21">
+      <c r="N21">
         <v>0.8158906444869857</v>
       </c>
-      <c r="N21">
+      <c r="O21">
         <v>0.838700290668682</v>
       </c>
-      <c r="O21">
+      <c r="P21">
         <v>0.8505503843683264</v>
       </c>
-      <c r="P21">
+      <c r="Q21">
         <v>0.8649105048308506</v>
       </c>
     </row>
@@ -1483,48 +1548,51 @@
         </is>
       </c>
       <c r="B22">
+        <v>0</v>
+      </c>
+      <c r="C22">
         <v>0.4773126277165801</v>
       </c>
-      <c r="C22">
+      <c r="D22">
         <v>0.5357212902283869</v>
       </c>
-      <c r="D22">
+      <c r="E22">
         <v>0.5700984722319169</v>
       </c>
-      <c r="E22">
+      <c r="F22">
         <v>0.6153400534395275</v>
       </c>
-      <c r="F22">
+      <c r="G22">
         <v>0.6737703901035814</v>
       </c>
-      <c r="G22">
+      <c r="H22">
         <v>0.6984794066947239</v>
       </c>
-      <c r="H22">
+      <c r="I22">
         <v>0.7244211034088037</v>
       </c>
-      <c r="I22">
+      <c r="J22">
         <v>0.73821436935858</v>
       </c>
-      <c r="J22">
+      <c r="K22">
         <v>0.7575435330187652</v>
       </c>
-      <c r="K22">
+      <c r="L22">
         <v>0.7832844962578642</v>
       </c>
-      <c r="L22">
+      <c r="M22">
         <v>0.7963344785480693</v>
       </c>
-      <c r="M22">
+      <c r="N22">
         <v>0.8239214341561789</v>
       </c>
-      <c r="N22">
+      <c r="O22">
         <v>0.8411723123965217</v>
       </c>
-      <c r="O22">
+      <c r="P22">
         <v>0.8531976902422045</v>
       </c>
-      <c r="P22">
+      <c r="Q22">
         <v>0.8692940192763912</v>
       </c>
     </row>
@@ -1535,1296 +1603,1151 @@
         </is>
       </c>
       <c r="B23">
+        <v>0</v>
+      </c>
+      <c r="C23">
         <v>0.523879171162677</v>
       </c>
-      <c r="C23">
+      <c r="D23">
         <v>0.5634900297868128</v>
       </c>
-      <c r="D23">
+      <c r="E23">
         <v>0.613719499641879</v>
       </c>
-      <c r="E23">
+      <c r="F23">
         <v>0.6303400363305518</v>
       </c>
-      <c r="F23">
+      <c r="G23">
         <v>0.6486828485059029</v>
       </c>
-      <c r="G23">
+      <c r="H23">
         <v>0.694741036521594</v>
       </c>
-      <c r="H23">
+      <c r="I23">
         <v>0.7165424300983479</v>
       </c>
-      <c r="I23">
+      <c r="J23">
         <v>0.7454394490573377</v>
       </c>
-      <c r="J23">
+      <c r="K23">
         <v>0.7697092246794819</v>
       </c>
-      <c r="K23">
+      <c r="L23">
         <v>0.8037985954498521</v>
       </c>
-      <c r="L23">
+      <c r="M23">
         <v>0.8243407457220651</v>
       </c>
-      <c r="M23">
+      <c r="N23">
         <v>0.8434338572513822</v>
       </c>
-      <c r="N23">
+      <c r="O23">
         <v>0.8612738124612109</v>
       </c>
-      <c r="O23">
+      <c r="P23">
         <v>0.8854958352846972</v>
       </c>
-      <c r="P23">
+      <c r="Q23">
         <v>0.9068818838322673</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>adj_red_c(950,20,1)_snv_sder_c(1,3,15)_</t>
+          <t>adj_ref2abs_red_c(1,1300,1)_msc_</t>
         </is>
       </c>
       <c r="B24">
-        <v>0.2026728725177539</v>
+        <v>0</v>
       </c>
       <c r="C24">
-        <v>0.2870787741056502</v>
+        <v>0.5729428440761467</v>
       </c>
       <c r="D24">
-        <v>0.3263020392958502</v>
+        <v>0.6488556997636949</v>
       </c>
       <c r="E24">
-        <v>0.379187936352307</v>
+        <v>0.6916442279537431</v>
       </c>
       <c r="F24">
-        <v>0.4279352929697445</v>
+        <v>0.7188257554302082</v>
       </c>
       <c r="G24">
-        <v>0.4835398215299741</v>
+        <v>0.7360742044087063</v>
       </c>
       <c r="H24">
-        <v>0.5518591897239608</v>
+        <v>0.7485049702592107</v>
       </c>
       <c r="I24">
-        <v>0.5928592881387796</v>
+        <v>0.7604266868805563</v>
       </c>
       <c r="J24">
-        <v>0.6380405130441091</v>
+        <v>0.7828669710695511</v>
       </c>
       <c r="K24">
-        <v>0.6694336810103452</v>
+        <v>0.8025138249535135</v>
       </c>
       <c r="L24">
-        <v>0.7059233669032926</v>
+        <v>0.8313419411657222</v>
       </c>
       <c r="M24">
-        <v>0.7446695768121472</v>
+        <v>0.8560206592670521</v>
       </c>
       <c r="N24">
-        <v>0.8013366731899559</v>
+        <v>0.8745074429961683</v>
       </c>
       <c r="O24">
-        <v>0.830688937736442</v>
+        <v>0.8888729712093499</v>
       </c>
       <c r="P24">
-        <v>0.8554770668849931</v>
+        <v>0.9050295008573596</v>
+      </c>
+      <c r="Q24">
+        <v>0.9207003972476087</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>adj_red_c(950,20,1)_snv_sder_c(2,3,15)_</t>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_</t>
         </is>
       </c>
       <c r="B25">
-        <v>0.1868339178194603</v>
+        <v>0</v>
       </c>
       <c r="C25">
-        <v>0.264213041668418</v>
+        <v>0.5717788916665263</v>
       </c>
       <c r="D25">
-        <v>0.3061865109351866</v>
+        <v>0.6523794213632965</v>
       </c>
       <c r="E25">
-        <v>0.378409151671717</v>
+        <v>0.7105743272284792</v>
       </c>
       <c r="F25">
-        <v>0.4638589003255582</v>
+        <v>0.7460844116244811</v>
       </c>
       <c r="G25">
-        <v>0.4993017653707463</v>
+        <v>0.7718548585185477</v>
       </c>
       <c r="H25">
-        <v>0.5531752497307856</v>
+        <v>0.781683443605877</v>
       </c>
       <c r="I25">
-        <v>0.6112617639025884</v>
+        <v>0.7851658503454301</v>
       </c>
       <c r="J25">
-        <v>0.6455413106931505</v>
+        <v>0.8208306404837098</v>
       </c>
       <c r="K25">
-        <v>0.6858724271121777</v>
+        <v>0.8272964587619339</v>
       </c>
       <c r="L25">
-        <v>0.7417259313088229</v>
+        <v>0.8541654248585575</v>
       </c>
       <c r="M25">
-        <v>0.7966955249018928</v>
+        <v>0.8678352635914993</v>
       </c>
       <c r="N25">
-        <v>0.8310147465757375</v>
+        <v>0.8826573718376862</v>
       </c>
       <c r="O25">
-        <v>0.8515778212208257</v>
+        <v>0.8990407331019319</v>
       </c>
       <c r="P25">
-        <v>0.8678943873730151</v>
+        <v>0.9077445821824861</v>
+      </c>
+      <c r="Q25">
+        <v>0.9277691299466952</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>adj_red_c(950,750,1)_snv_sder_c(1,3,15)_</t>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_detr_2_</t>
         </is>
       </c>
       <c r="B26">
-        <v>0.1720643114704661</v>
+        <v>0</v>
       </c>
       <c r="C26">
-        <v>0.221808467903199</v>
+        <v>0.5867775213289101</v>
       </c>
       <c r="D26">
-        <v>0.2592871809045681</v>
+        <v>0.6343105764301229</v>
       </c>
       <c r="E26">
-        <v>0.3007730327425786</v>
+        <v>0.7051498384448702</v>
       </c>
       <c r="F26">
-        <v>0.3526548221369555</v>
+        <v>0.7280927031314202</v>
       </c>
       <c r="G26">
-        <v>0.3876646477051519</v>
+        <v>0.7495803153009044</v>
       </c>
       <c r="H26">
-        <v>0.4198398082837145</v>
+        <v>0.7640718774986168</v>
       </c>
       <c r="I26">
-        <v>0.4696026049942083</v>
+        <v>0.7758464495408631</v>
       </c>
       <c r="J26">
-        <v>0.5161270496632053</v>
+        <v>0.7933144259296281</v>
       </c>
       <c r="K26">
-        <v>0.5705128390703122</v>
+        <v>0.831907618464691</v>
       </c>
       <c r="L26">
-        <v>0.6075558565854752</v>
+        <v>0.8595670392321343</v>
       </c>
       <c r="M26">
-        <v>0.6381534783509917</v>
+        <v>0.8778058000087192</v>
       </c>
       <c r="N26">
-        <v>0.6714010432665212</v>
+        <v>0.891619450050385</v>
       </c>
       <c r="O26">
-        <v>0.7113564625173379</v>
+        <v>0.9017989137956818</v>
       </c>
       <c r="P26">
-        <v>0.7332162554404401</v>
+        <v>0.9196038985480973</v>
+      </c>
+      <c r="Q26">
+        <v>0.9287288093626801</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>adj_red_c(950,750,1)_snv_sder_c(2,3,15)_</t>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_detr_2_sder_c(0,3,21)_</t>
         </is>
       </c>
       <c r="B27">
-        <v>0.1532486003542978</v>
+        <v>0</v>
       </c>
       <c r="C27">
-        <v>0.2082811182978614</v>
+        <v>0.5867453144322022</v>
       </c>
       <c r="D27">
-        <v>0.3305327095875755</v>
+        <v>0.6340807845920118</v>
       </c>
       <c r="E27">
-        <v>0.3465772989553334</v>
+        <v>0.7044652536413817</v>
       </c>
       <c r="F27">
-        <v>0.4194780399004011</v>
+        <v>0.7260158022588629</v>
       </c>
       <c r="G27">
-        <v>0.4737957786142609</v>
+        <v>0.7469668483977479</v>
       </c>
       <c r="H27">
-        <v>0.5289941070869226</v>
+        <v>0.7588195315469037</v>
       </c>
       <c r="I27">
-        <v>0.5647358448985169</v>
+        <v>0.7657148876829128</v>
       </c>
       <c r="J27">
-        <v>0.6285759105469628</v>
+        <v>0.7737315194615766</v>
       </c>
       <c r="K27">
-        <v>0.6496205627375554</v>
+        <v>0.7821626923197781</v>
       </c>
       <c r="L27">
-        <v>0.6674362433860603</v>
+        <v>0.7906625545367597</v>
       </c>
       <c r="M27">
-        <v>0.7261002231613628</v>
+        <v>0.7963742743578059</v>
       </c>
       <c r="N27">
-        <v>0.7511994120676128</v>
+        <v>0.8082894252687119</v>
       </c>
       <c r="O27">
-        <v>0.7803995234877157</v>
+        <v>0.8134219998056842</v>
       </c>
       <c r="P27">
-        <v>0.79858411233983</v>
+        <v>0.8267222402521959</v>
+      </c>
+      <c r="Q27">
+        <v>0.841882765781786</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_msc_</t>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,21)_</t>
         </is>
       </c>
       <c r="B28">
-        <v>0.5729428440761467</v>
+        <v>0</v>
       </c>
       <c r="C28">
-        <v>0.6488556997636949</v>
+        <v>0.5717033021208531</v>
       </c>
       <c r="D28">
-        <v>0.6916442279537431</v>
+        <v>0.6522290544805762</v>
       </c>
       <c r="E28">
-        <v>0.7188257554302082</v>
+        <v>0.7099826691825799</v>
       </c>
       <c r="F28">
-        <v>0.7360742044087063</v>
+        <v>0.7455822139418875</v>
       </c>
       <c r="G28">
-        <v>0.7485049702592107</v>
+        <v>0.7701380407442731</v>
       </c>
       <c r="H28">
-        <v>0.7604266868805563</v>
+        <v>0.7782287687054754</v>
       </c>
       <c r="I28">
-        <v>0.7828669710695511</v>
+        <v>0.78031430952181</v>
       </c>
       <c r="J28">
-        <v>0.8025138249535135</v>
+        <v>0.7969672477820785</v>
       </c>
       <c r="K28">
-        <v>0.8313419411657222</v>
+        <v>0.7990961849040711</v>
       </c>
       <c r="L28">
-        <v>0.8560206592670521</v>
+        <v>0.8039746397529043</v>
       </c>
       <c r="M28">
-        <v>0.8745074429961683</v>
+        <v>0.806739050911883</v>
       </c>
       <c r="N28">
-        <v>0.8888729712093499</v>
+        <v>0.8171541097179025</v>
       </c>
       <c r="O28">
-        <v>0.9050295008573596</v>
+        <v>0.8208182933422417</v>
       </c>
       <c r="P28">
-        <v>0.9207003972476087</v>
+        <v>0.8267735154800504</v>
+      </c>
+      <c r="Q28">
+        <v>0.8368259169008883</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_snv_</t>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,25)_</t>
         </is>
       </c>
       <c r="B29">
-        <v>0.5717788916665263</v>
+        <v>0</v>
       </c>
       <c r="C29">
-        <v>0.6523794213632965</v>
+        <v>0.5716209479922364</v>
       </c>
       <c r="D29">
-        <v>0.7105743272284792</v>
+        <v>0.6522264102733444</v>
       </c>
       <c r="E29">
-        <v>0.7460844116244811</v>
+        <v>0.7098452811350615</v>
       </c>
       <c r="F29">
-        <v>0.7718548585185477</v>
+        <v>0.7455713373274809</v>
       </c>
       <c r="G29">
-        <v>0.781683443605877</v>
+        <v>0.7700510369027654</v>
       </c>
       <c r="H29">
-        <v>0.7851658503454301</v>
+        <v>0.7780087882863765</v>
       </c>
       <c r="I29">
-        <v>0.8208306404837098</v>
+        <v>0.7800227159527057</v>
       </c>
       <c r="J29">
-        <v>0.8272964587619339</v>
+        <v>0.795836436391657</v>
       </c>
       <c r="K29">
-        <v>0.8541654248585575</v>
+        <v>0.79805181577819</v>
       </c>
       <c r="L29">
-        <v>0.8678352635914993</v>
+        <v>0.8022385349795409</v>
       </c>
       <c r="M29">
-        <v>0.8826573718376862</v>
+        <v>0.8041313960555071</v>
       </c>
       <c r="N29">
-        <v>0.8990407331019319</v>
+        <v>0.8118934155699071</v>
       </c>
       <c r="O29">
-        <v>0.9077445821824861</v>
+        <v>0.8150626270878231</v>
       </c>
       <c r="P29">
-        <v>0.9277691299466952</v>
+        <v>0.8191698126092721</v>
+      </c>
+      <c r="Q29">
+        <v>0.8255298424946809</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_snv_detr_2_</t>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,27)_</t>
         </is>
       </c>
       <c r="B30">
-        <v>0.5867775213289101</v>
+        <v>0</v>
       </c>
       <c r="C30">
-        <v>0.6343105764301229</v>
+        <v>0.5715642784449799</v>
       </c>
       <c r="D30">
-        <v>0.7051498384448702</v>
+        <v>0.6522383885847434</v>
       </c>
       <c r="E30">
-        <v>0.7280927031314202</v>
+        <v>0.7097692350561653</v>
       </c>
       <c r="F30">
-        <v>0.7495803153009044</v>
+        <v>0.7455633882012163</v>
       </c>
       <c r="G30">
-        <v>0.7640718774986168</v>
+        <v>0.7700051975979756</v>
       </c>
       <c r="H30">
-        <v>0.7758464495408631</v>
+        <v>0.7779047231681084</v>
       </c>
       <c r="I30">
-        <v>0.7933144259296281</v>
+        <v>0.7798886662568785</v>
       </c>
       <c r="J30">
-        <v>0.831907618464691</v>
+        <v>0.7953334990426687</v>
       </c>
       <c r="K30">
-        <v>0.8595670392321343</v>
+        <v>0.7976857924975644</v>
       </c>
       <c r="L30">
-        <v>0.8778058000087192</v>
+        <v>0.801844801332654</v>
       </c>
       <c r="M30">
-        <v>0.891619450050385</v>
+        <v>0.8035548174239476</v>
       </c>
       <c r="N30">
-        <v>0.9017989137956818</v>
+        <v>0.810269307643533</v>
       </c>
       <c r="O30">
-        <v>0.9196038985480973</v>
+        <v>0.813295030475613</v>
       </c>
       <c r="P30">
-        <v>0.9287288093626801</v>
+        <v>0.8168758478697881</v>
+      </c>
+      <c r="Q30">
+        <v>0.8214550466567153</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_snv_detr_2_sder_c(0,3,21)_</t>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,31)_</t>
         </is>
       </c>
       <c r="B31">
-        <v>0.5867453144322022</v>
+        <v>0</v>
       </c>
       <c r="C31">
-        <v>0.6340807845920118</v>
+        <v>0.5714233077140054</v>
       </c>
       <c r="D31">
-        <v>0.7044652536413817</v>
+        <v>0.6522709175382165</v>
       </c>
       <c r="E31">
-        <v>0.7260158022588629</v>
+        <v>0.7095992289129885</v>
       </c>
       <c r="F31">
-        <v>0.7469668483977479</v>
+        <v>0.7456035298443193</v>
       </c>
       <c r="G31">
-        <v>0.7588195315469037</v>
+        <v>0.7699779569047632</v>
       </c>
       <c r="H31">
-        <v>0.7657148876829128</v>
+        <v>0.777727348611127</v>
       </c>
       <c r="I31">
-        <v>0.7737315194615766</v>
+        <v>0.7796536200749737</v>
       </c>
       <c r="J31">
-        <v>0.7821626923197781</v>
+        <v>0.7943988959571268</v>
       </c>
       <c r="K31">
-        <v>0.7906625545367597</v>
+        <v>0.7972002781835845</v>
       </c>
       <c r="L31">
-        <v>0.7963742743578059</v>
+        <v>0.8017527124838404</v>
       </c>
       <c r="M31">
-        <v>0.8082894252687119</v>
+        <v>0.8036161909484767</v>
       </c>
       <c r="N31">
-        <v>0.8134219998056842</v>
+        <v>0.8098899273922264</v>
       </c>
       <c r="O31">
-        <v>0.8267222402521959</v>
+        <v>0.8134452743122396</v>
       </c>
       <c r="P31">
-        <v>0.841882765781786</v>
+        <v>0.8183227938673183</v>
+      </c>
+      <c r="Q31">
+        <v>0.8243595195078312</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,21)_</t>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,15)_</t>
         </is>
       </c>
       <c r="B32">
-        <v>0.5717033021208531</v>
+        <v>0</v>
       </c>
       <c r="C32">
-        <v>0.6522290544805762</v>
+        <v>0.5717636327602994</v>
       </c>
       <c r="D32">
-        <v>0.7099826691825799</v>
+        <v>0.6522304942461368</v>
       </c>
       <c r="E32">
-        <v>0.7455822139418875</v>
+        <v>0.7101552340753154</v>
       </c>
       <c r="F32">
-        <v>0.7701380407442731</v>
+        <v>0.7456496159071224</v>
       </c>
       <c r="G32">
-        <v>0.7782287687054754</v>
+        <v>0.7703503698492398</v>
       </c>
       <c r="H32">
-        <v>0.78031430952181</v>
+        <v>0.7785984888530526</v>
       </c>
       <c r="I32">
-        <v>0.7969672477820785</v>
+        <v>0.7808320502640214</v>
       </c>
       <c r="J32">
-        <v>0.7990961849040711</v>
+        <v>0.7990584878118482</v>
       </c>
       <c r="K32">
-        <v>0.8039746397529043</v>
+        <v>0.8013909611907531</v>
       </c>
       <c r="L32">
-        <v>0.806739050911883</v>
+        <v>0.808439414299988</v>
       </c>
       <c r="M32">
-        <v>0.8171541097179025</v>
+        <v>0.813452371059932</v>
       </c>
       <c r="N32">
-        <v>0.8208182933422417</v>
+        <v>0.82681472184828</v>
       </c>
       <c r="O32">
-        <v>0.8267735154800504</v>
+        <v>0.8307354820239601</v>
       </c>
       <c r="P32">
-        <v>0.8368259169008883</v>
+        <v>0.8377448128770338</v>
+      </c>
+      <c r="Q32">
+        <v>0.8502158088614483</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,25)_</t>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,17)_</t>
         </is>
       </c>
       <c r="B33">
-        <v>0.5716209479922364</v>
+        <v>0</v>
       </c>
       <c r="C33">
-        <v>0.6522264102733444</v>
+        <v>0.5717493697866226</v>
       </c>
       <c r="D33">
-        <v>0.7098452811350615</v>
+        <v>0.6522284732683925</v>
       </c>
       <c r="E33">
-        <v>0.7455713373274809</v>
+        <v>0.7101167810214264</v>
       </c>
       <c r="F33">
-        <v>0.7700510369027654</v>
+        <v>0.7456287282029089</v>
       </c>
       <c r="G33">
-        <v>0.7780087882863765</v>
+        <v>0.7702587032907703</v>
       </c>
       <c r="H33">
-        <v>0.7800227159527057</v>
+        <v>0.7784223433358521</v>
       </c>
       <c r="I33">
-        <v>0.795836436391657</v>
+        <v>0.7806129402680404</v>
       </c>
       <c r="J33">
-        <v>0.79805181577819</v>
+        <v>0.7981711104772198</v>
       </c>
       <c r="K33">
-        <v>0.8022385349795409</v>
+        <v>0.8003537444754554</v>
       </c>
       <c r="L33">
-        <v>0.8041313960555071</v>
+        <v>0.8061899712328021</v>
       </c>
       <c r="M33">
-        <v>0.8118934155699071</v>
+        <v>0.8101615090677846</v>
       </c>
       <c r="N33">
-        <v>0.8150626270878231</v>
+        <v>0.8229786761042397</v>
       </c>
       <c r="O33">
-        <v>0.8191698126092721</v>
+        <v>0.8266419751265319</v>
       </c>
       <c r="P33">
-        <v>0.8255298424946809</v>
+        <v>0.8329588363442247</v>
+      </c>
+      <c r="Q33">
+        <v>0.8441500325994205</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,27)_</t>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,19)_</t>
         </is>
       </c>
       <c r="B34">
-        <v>0.5715642784449799</v>
+        <v>0</v>
       </c>
       <c r="C34">
-        <v>0.6522383885847434</v>
+        <v>0.5717294267598338</v>
       </c>
       <c r="D34">
-        <v>0.7097692350561653</v>
+        <v>0.6522368277691877</v>
       </c>
       <c r="E34">
-        <v>0.7455633882012163</v>
+        <v>0.7100724200646459</v>
       </c>
       <c r="F34">
-        <v>0.7700051975979756</v>
+        <v>0.7456050021350001</v>
       </c>
       <c r="G34">
-        <v>0.7779047231681084</v>
+        <v>0.7701882613899853</v>
       </c>
       <c r="H34">
-        <v>0.7798886662568785</v>
+        <v>0.7782948382858192</v>
       </c>
       <c r="I34">
-        <v>0.7953334990426687</v>
+        <v>0.7804571114916385</v>
       </c>
       <c r="J34">
-        <v>0.7976857924975644</v>
+        <v>0.7975871803000539</v>
       </c>
       <c r="K34">
-        <v>0.801844801332654</v>
+        <v>0.799734457225497</v>
       </c>
       <c r="L34">
-        <v>0.8035548174239476</v>
+        <v>0.8048857667817182</v>
       </c>
       <c r="M34">
-        <v>0.810269307643533</v>
+        <v>0.8082290833625696</v>
       </c>
       <c r="N34">
-        <v>0.813295030475613</v>
+        <v>0.820316093373233</v>
       </c>
       <c r="O34">
-        <v>0.8168758478697881</v>
+        <v>0.8238885132241804</v>
       </c>
       <c r="P34">
-        <v>0.8214550466567153</v>
+        <v>0.8298475356411923</v>
+      </c>
+      <c r="Q34">
+        <v>0.8402303205494044</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,31)_</t>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,21)_</t>
         </is>
       </c>
       <c r="B35">
-        <v>0.5714233077140054</v>
+        <v>0</v>
       </c>
       <c r="C35">
-        <v>0.6522709175382165</v>
+        <v>0.5717029829508558</v>
       </c>
       <c r="D35">
-        <v>0.7095992289129885</v>
+        <v>0.6522578016415346</v>
       </c>
       <c r="E35">
-        <v>0.7456035298443193</v>
+        <v>0.7100391843125218</v>
       </c>
       <c r="F35">
-        <v>0.7699779569047632</v>
+        <v>0.7455821792014055</v>
       </c>
       <c r="G35">
-        <v>0.777727348611127</v>
+        <v>0.7701202228697513</v>
       </c>
       <c r="H35">
-        <v>0.7796536200749737</v>
+        <v>0.7781645878975667</v>
       </c>
       <c r="I35">
-        <v>0.7943988959571268</v>
+        <v>0.7803140039651784</v>
       </c>
       <c r="J35">
-        <v>0.7972002781835845</v>
+        <v>0.7970300508315182</v>
       </c>
       <c r="K35">
-        <v>0.8017527124838404</v>
+        <v>0.799183609370127</v>
       </c>
       <c r="L35">
-        <v>0.8036161909484767</v>
+        <v>0.8039173156377136</v>
       </c>
       <c r="M35">
-        <v>0.8098899273922264</v>
+        <v>0.8067756936250844</v>
       </c>
       <c r="N35">
-        <v>0.8134452743122396</v>
+        <v>0.8178333421582832</v>
       </c>
       <c r="O35">
-        <v>0.8183227938673183</v>
+        <v>0.8213808020692175</v>
       </c>
       <c r="P35">
-        <v>0.8243595195078312</v>
+        <v>0.8273330199214471</v>
+      </c>
+      <c r="Q35">
+        <v>0.8383459240045409</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,15)_</t>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,31)_</t>
         </is>
       </c>
       <c r="B36">
-        <v>0.5717636327602994</v>
+        <v>0</v>
       </c>
       <c r="C36">
-        <v>0.6522304942461368</v>
+        <v>0.5714299841624246</v>
       </c>
       <c r="D36">
-        <v>0.7101552340753154</v>
+        <v>0.6523378479480337</v>
       </c>
       <c r="E36">
-        <v>0.7456496159071224</v>
+        <v>0.7095939557080213</v>
       </c>
       <c r="F36">
-        <v>0.7703503698492398</v>
+        <v>0.7454948646457134</v>
       </c>
       <c r="G36">
-        <v>0.7785984888530526</v>
+        <v>0.7699089544277598</v>
       </c>
       <c r="H36">
-        <v>0.7808320502640214</v>
+        <v>0.7776169604507739</v>
       </c>
       <c r="I36">
-        <v>0.7990584878118482</v>
+        <v>0.7796527125515542</v>
       </c>
       <c r="J36">
-        <v>0.8013909611907531</v>
+        <v>0.7943879543643837</v>
       </c>
       <c r="K36">
-        <v>0.808439414299988</v>
+        <v>0.7972043100073798</v>
       </c>
       <c r="L36">
-        <v>0.813452371059932</v>
+        <v>0.8019586558066895</v>
       </c>
       <c r="M36">
-        <v>0.82681472184828</v>
+        <v>0.8047000271166163</v>
       </c>
       <c r="N36">
-        <v>0.8307354820239601</v>
+        <v>0.8106715466632662</v>
       </c>
       <c r="O36">
-        <v>0.8377448128770338</v>
+        <v>0.8138648315238852</v>
       </c>
       <c r="P36">
-        <v>0.8502158088614483</v>
+        <v>0.8189243618523114</v>
+      </c>
+      <c r="Q36">
+        <v>0.8232581640425598</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,17)_</t>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(1,3,15)_</t>
         </is>
       </c>
       <c r="B37">
-        <v>0.5717493697866226</v>
+        <v>0</v>
       </c>
       <c r="C37">
-        <v>0.6522284732683925</v>
+        <v>0.5847500753555446</v>
       </c>
       <c r="D37">
-        <v>0.7101167810214264</v>
+        <v>0.7174862460484219</v>
       </c>
       <c r="E37">
-        <v>0.7456287282029089</v>
+        <v>0.7393774727243541</v>
       </c>
       <c r="F37">
-        <v>0.7702587032907703</v>
+        <v>0.7643249265839083</v>
       </c>
       <c r="G37">
-        <v>0.7784223433358521</v>
+        <v>0.7913620166714692</v>
       </c>
       <c r="H37">
-        <v>0.7806129402680404</v>
+        <v>0.813085686867239</v>
       </c>
       <c r="I37">
-        <v>0.7981711104772198</v>
+        <v>0.8322860749063044</v>
       </c>
       <c r="J37">
-        <v>0.8003537444754554</v>
+        <v>0.8426230418841751</v>
       </c>
       <c r="K37">
-        <v>0.8061899712328021</v>
+        <v>0.8555674324106763</v>
       </c>
       <c r="L37">
-        <v>0.8101615090677846</v>
+        <v>0.8720053895889537</v>
       </c>
       <c r="M37">
-        <v>0.8229786761042397</v>
+        <v>0.8846566073506649</v>
       </c>
       <c r="N37">
-        <v>0.8266419751265319</v>
+        <v>0.8937482192281286</v>
       </c>
       <c r="O37">
-        <v>0.8329588363442247</v>
+        <v>0.9058947984034004</v>
       </c>
       <c r="P37">
-        <v>0.8441500325994205</v>
+        <v>0.9126251513865256</v>
+      </c>
+      <c r="Q37">
+        <v>0.9173988678105061</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,19)_</t>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(1,3,25)_</t>
         </is>
       </c>
       <c r="B38">
-        <v>0.5717294267598338</v>
+        <v>0</v>
       </c>
       <c r="C38">
-        <v>0.6522368277691877</v>
+        <v>0.5857520175578081</v>
       </c>
       <c r="D38">
-        <v>0.7100724200646459</v>
+        <v>0.7122759821976079</v>
       </c>
       <c r="E38">
-        <v>0.7456050021350001</v>
+        <v>0.7326336562528772</v>
       </c>
       <c r="F38">
-        <v>0.7701882613899853</v>
+        <v>0.7470725237974809</v>
       </c>
       <c r="G38">
-        <v>0.7782948382858192</v>
+        <v>0.7568669769996023</v>
       </c>
       <c r="H38">
-        <v>0.7804571114916385</v>
+        <v>0.7861967453483918</v>
       </c>
       <c r="I38">
-        <v>0.7975871803000539</v>
+        <v>0.7984414426075234</v>
       </c>
       <c r="J38">
-        <v>0.799734457225497</v>
+        <v>0.8076188400230276</v>
       </c>
       <c r="K38">
-        <v>0.8048857667817182</v>
+        <v>0.8182676694367299</v>
       </c>
       <c r="L38">
-        <v>0.8082290833625696</v>
+        <v>0.8274086350874247</v>
       </c>
       <c r="M38">
-        <v>0.820316093373233</v>
+        <v>0.8337663832424316</v>
       </c>
       <c r="N38">
-        <v>0.8238885132241804</v>
+        <v>0.8473171159751448</v>
       </c>
       <c r="O38">
-        <v>0.8298475356411923</v>
+        <v>0.8617249880642368</v>
       </c>
       <c r="P38">
-        <v>0.8402303205494044</v>
+        <v>0.8785953556317407</v>
+      </c>
+      <c r="Q38">
+        <v>0.8919807410924105</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,21)_</t>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(1,3,31)_</t>
         </is>
       </c>
       <c r="B39">
-        <v>0.5717029829508558</v>
+        <v>0</v>
       </c>
       <c r="C39">
-        <v>0.6522578016415346</v>
+        <v>0.5863269768512813</v>
       </c>
       <c r="D39">
-        <v>0.7100391843125218</v>
+        <v>0.7121913853554148</v>
       </c>
       <c r="E39">
-        <v>0.7455821792014055</v>
+        <v>0.7301671982758701</v>
       </c>
       <c r="F39">
-        <v>0.7701202228697513</v>
+        <v>0.7444653345619371</v>
       </c>
       <c r="G39">
-        <v>0.7781645878975667</v>
+        <v>0.752787932712944</v>
       </c>
       <c r="H39">
-        <v>0.7803140039651784</v>
+        <v>0.7742572683874523</v>
       </c>
       <c r="I39">
-        <v>0.7970300508315182</v>
+        <v>0.7830024202105641</v>
       </c>
       <c r="J39">
-        <v>0.799183609370127</v>
+        <v>0.7876475445219644</v>
       </c>
       <c r="K39">
-        <v>0.8039173156377136</v>
+        <v>0.7956314997992699</v>
       </c>
       <c r="L39">
-        <v>0.8067756936250844</v>
+        <v>0.8044140118510126</v>
       </c>
       <c r="M39">
-        <v>0.8178333421582832</v>
+        <v>0.8085062712952189</v>
       </c>
       <c r="N39">
-        <v>0.8213808020692175</v>
+        <v>0.8291188199095043</v>
       </c>
       <c r="O39">
-        <v>0.8273330199214471</v>
+        <v>0.8407237170043309</v>
       </c>
       <c r="P39">
-        <v>0.8383459240045409</v>
+        <v>0.860855577796069</v>
+      </c>
+      <c r="Q39">
+        <v>0.8750640537237216</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,31)_</t>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(2,3,21)_</t>
         </is>
       </c>
       <c r="B40">
-        <v>0.5714299841624246</v>
+        <v>0</v>
       </c>
       <c r="C40">
-        <v>0.6523378479480337</v>
+        <v>0.5477484828108743</v>
       </c>
       <c r="D40">
-        <v>0.7095939557080213</v>
+        <v>0.5785302290283678</v>
       </c>
       <c r="E40">
-        <v>0.7454948646457134</v>
+        <v>0.637159678449339</v>
       </c>
       <c r="F40">
-        <v>0.7699089544277598</v>
+        <v>0.6847268951865977</v>
       </c>
       <c r="G40">
-        <v>0.7776169604507739</v>
+        <v>0.750899619270764</v>
       </c>
       <c r="H40">
-        <v>0.7796527125515542</v>
+        <v>0.7766922766936539</v>
       </c>
       <c r="I40">
-        <v>0.7943879543643837</v>
+        <v>0.794056441247724</v>
       </c>
       <c r="J40">
-        <v>0.7972043100073798</v>
+        <v>0.8063861241809853</v>
       </c>
       <c r="K40">
-        <v>0.8019586558066895</v>
+        <v>0.8190030474752482</v>
       </c>
       <c r="L40">
-        <v>0.8047000271166163</v>
+        <v>0.8345883282064048</v>
       </c>
       <c r="M40">
-        <v>0.8106715466632662</v>
+        <v>0.8502217755090888</v>
       </c>
       <c r="N40">
-        <v>0.8138648315238852</v>
+        <v>0.8640270981237334</v>
       </c>
       <c r="O40">
-        <v>0.8189243618523114</v>
+        <v>0.875681912331892</v>
       </c>
       <c r="P40">
-        <v>0.8232581640425598</v>
+        <v>0.8882865234656292</v>
+      </c>
+      <c r="Q40">
+        <v>0.8992184334655807</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(1,3,15)_</t>
+          <t>adj_snv_sder_c(1,3,5)_</t>
         </is>
       </c>
       <c r="B41">
-        <v>0.5847500753555446</v>
+        <v>0</v>
       </c>
       <c r="C41">
-        <v>0.7174862460484219</v>
+        <v>0.5326470300745866</v>
       </c>
       <c r="D41">
-        <v>0.7393774727243541</v>
+        <v>0.5848912403224964</v>
       </c>
       <c r="E41">
-        <v>0.7643249265839083</v>
+        <v>0.6302321254062571</v>
       </c>
       <c r="F41">
-        <v>0.7913620166714692</v>
+        <v>0.6758241933937001</v>
       </c>
       <c r="G41">
-        <v>0.813085686867239</v>
+        <v>0.7425740075640954</v>
       </c>
       <c r="H41">
-        <v>0.8322860749063044</v>
+        <v>0.7896952444673582</v>
       </c>
       <c r="I41">
-        <v>0.8426230418841751</v>
+        <v>0.8004950165968689</v>
       </c>
       <c r="J41">
-        <v>0.8555674324106763</v>
+        <v>0.8165644466485104</v>
       </c>
       <c r="K41">
-        <v>0.8720053895889537</v>
+        <v>0.8416506181964096</v>
       </c>
       <c r="L41">
-        <v>0.8846566073506649</v>
+        <v>0.8554420971074601</v>
       </c>
       <c r="M41">
-        <v>0.8937482192281286</v>
+        <v>0.8756291589004875</v>
       </c>
       <c r="N41">
-        <v>0.9058947984034004</v>
+        <v>0.8934347026321993</v>
       </c>
       <c r="O41">
-        <v>0.9126251513865256</v>
+        <v>0.9183442557477342</v>
       </c>
       <c r="P41">
-        <v>0.9173988678105061</v>
+        <v>0.9319250834428303</v>
+      </c>
+      <c r="Q41">
+        <v>0.9414280453434519</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(1,3,25)_</t>
+          <t>adj_snv_sder_c(2,3,15)_</t>
         </is>
       </c>
       <c r="B42">
-        <v>0.5857520175578081</v>
+        <v>0</v>
       </c>
       <c r="C42">
-        <v>0.7122759821976079</v>
+        <v>0.493848972025361</v>
       </c>
       <c r="D42">
-        <v>0.7326336562528772</v>
+        <v>0.5632330643944614</v>
       </c>
       <c r="E42">
-        <v>0.7470725237974809</v>
+        <v>0.6183416884814877</v>
       </c>
       <c r="F42">
-        <v>0.7568669769996023</v>
+        <v>0.6657979268864257</v>
       </c>
       <c r="G42">
-        <v>0.7861967453483918</v>
+        <v>0.7333500580744727</v>
       </c>
       <c r="H42">
-        <v>0.7984414426075234</v>
+        <v>0.7477117759630771</v>
       </c>
       <c r="I42">
-        <v>0.8076188400230276</v>
+        <v>0.7747383005399713</v>
       </c>
       <c r="J42">
-        <v>0.8182676694367299</v>
+        <v>0.8064707989065623</v>
       </c>
       <c r="K42">
-        <v>0.8274086350874247</v>
+        <v>0.8230320442939307</v>
       </c>
       <c r="L42">
-        <v>0.8337663832424316</v>
+        <v>0.8511105720870362</v>
       </c>
       <c r="M42">
-        <v>0.8473171159751448</v>
+        <v>0.8706004616180726</v>
       </c>
       <c r="N42">
-        <v>0.8617249880642368</v>
+        <v>0.8970479057693777</v>
       </c>
       <c r="O42">
-        <v>0.8785953556317407</v>
+        <v>0.9059513182578967</v>
       </c>
       <c r="P42">
-        <v>0.8919807410924105</v>
+        <v>0.916887097528661</v>
+      </c>
+      <c r="Q42">
+        <v>0.9269650541789309</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(1,3,31)_</t>
+          <t>snv_sder_c(1,3,9)_red_c(10,10,1)_</t>
         </is>
       </c>
       <c r="B43">
-        <v>0.5863269768512813</v>
+        <v>0</v>
       </c>
       <c r="C43">
-        <v>0.7121913853554148</v>
+        <v>0.5513835615937731</v>
       </c>
       <c r="D43">
-        <v>0.7301671982758701</v>
+        <v>0.5937654499249638</v>
       </c>
       <c r="E43">
-        <v>0.7444653345619371</v>
+        <v>0.6206163136023782</v>
       </c>
       <c r="F43">
-        <v>0.752787932712944</v>
+        <v>0.6636935388879551</v>
       </c>
       <c r="G43">
-        <v>0.7742572683874523</v>
+        <v>0.7511693179212675</v>
       </c>
       <c r="H43">
-        <v>0.7830024202105641</v>
+        <v>0.7831359031025733</v>
       </c>
       <c r="I43">
-        <v>0.7876475445219644</v>
+        <v>0.8039698677329381</v>
       </c>
       <c r="J43">
-        <v>0.7956314997992699</v>
+        <v>0.8309401609815138</v>
       </c>
       <c r="K43">
-        <v>0.8044140118510126</v>
+        <v>0.8556973560851393</v>
       </c>
       <c r="L43">
-        <v>0.8085062712952189</v>
+        <v>0.8870886374647785</v>
       </c>
       <c r="M43">
-        <v>0.8291188199095043</v>
+        <v>0.9116029094920303</v>
       </c>
       <c r="N43">
-        <v>0.8407237170043309</v>
+        <v>0.926328412427</v>
       </c>
       <c r="O43">
-        <v>0.860855577796069</v>
+        <v>0.9323724169282548</v>
       </c>
       <c r="P43">
-        <v>0.8750640537237216</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(2,3,21)_</t>
-        </is>
-      </c>
-      <c r="B44">
-        <v>0.5477484828108743</v>
-      </c>
-      <c r="C44">
-        <v>0.5785302290283678</v>
-      </c>
-      <c r="D44">
-        <v>0.637159678449339</v>
-      </c>
-      <c r="E44">
-        <v>0.6847268951865977</v>
-      </c>
-      <c r="F44">
-        <v>0.750899619270764</v>
-      </c>
-      <c r="G44">
-        <v>0.7766922766936539</v>
-      </c>
-      <c r="H44">
-        <v>0.794056441247724</v>
-      </c>
-      <c r="I44">
-        <v>0.8063861241809853</v>
-      </c>
-      <c r="J44">
-        <v>0.8190030474752482</v>
-      </c>
-      <c r="K44">
-        <v>0.8345883282064048</v>
-      </c>
-      <c r="L44">
-        <v>0.8502217755090888</v>
-      </c>
-      <c r="M44">
-        <v>0.8640270981237334</v>
-      </c>
-      <c r="N44">
-        <v>0.875681912331892</v>
-      </c>
-      <c r="O44">
-        <v>0.8882865234656292</v>
-      </c>
-      <c r="P44">
-        <v>0.8992184334655807</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>adj_snv_sder_c(1,3,5)_</t>
-        </is>
-      </c>
-      <c r="B45">
-        <v>0.5326470300745866</v>
-      </c>
-      <c r="C45">
-        <v>0.5848912403224964</v>
-      </c>
-      <c r="D45">
-        <v>0.6302321254062571</v>
-      </c>
-      <c r="E45">
-        <v>0.6758241933937001</v>
-      </c>
-      <c r="F45">
-        <v>0.7425740075640954</v>
-      </c>
-      <c r="G45">
-        <v>0.7896952444673582</v>
-      </c>
-      <c r="H45">
-        <v>0.8004950165968689</v>
-      </c>
-      <c r="I45">
-        <v>0.8165644466485104</v>
-      </c>
-      <c r="J45">
-        <v>0.8416506181964096</v>
-      </c>
-      <c r="K45">
-        <v>0.8554420971074601</v>
-      </c>
-      <c r="L45">
-        <v>0.8756291589004875</v>
-      </c>
-      <c r="M45">
-        <v>0.8934347026321993</v>
-      </c>
-      <c r="N45">
-        <v>0.9183442557477342</v>
-      </c>
-      <c r="O45">
-        <v>0.9319250834428303</v>
-      </c>
-      <c r="P45">
-        <v>0.9414280453434519</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>adj_snv_sder_c(2,3,15)_</t>
-        </is>
-      </c>
-      <c r="B46">
-        <v>0.493848972025361</v>
-      </c>
-      <c r="C46">
-        <v>0.5632330643944614</v>
-      </c>
-      <c r="D46">
-        <v>0.6183416884814877</v>
-      </c>
-      <c r="E46">
-        <v>0.6657979268864257</v>
-      </c>
-      <c r="F46">
-        <v>0.7333500580744727</v>
-      </c>
-      <c r="G46">
-        <v>0.7477117759630771</v>
-      </c>
-      <c r="H46">
-        <v>0.7747383005399713</v>
-      </c>
-      <c r="I46">
-        <v>0.8064707989065623</v>
-      </c>
-      <c r="J46">
-        <v>0.8230320442939307</v>
-      </c>
-      <c r="K46">
-        <v>0.8511105720870362</v>
-      </c>
-      <c r="L46">
-        <v>0.8706004616180726</v>
-      </c>
-      <c r="M46">
-        <v>0.8970479057693777</v>
-      </c>
-      <c r="N46">
-        <v>0.9059513182578967</v>
-      </c>
-      <c r="O46">
-        <v>0.916887097528661</v>
-      </c>
-      <c r="P46">
-        <v>0.9269650541789309</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>snv_sder_c(1,3,9)_red_c(10,10,1)_</t>
-        </is>
-      </c>
-      <c r="B47">
-        <v>0.5513835615937731</v>
-      </c>
-      <c r="C47">
-        <v>0.5937654499249638</v>
-      </c>
-      <c r="D47">
-        <v>0.6206163136023782</v>
-      </c>
-      <c r="E47">
-        <v>0.6636935388879551</v>
-      </c>
-      <c r="F47">
-        <v>0.7511693179212675</v>
-      </c>
-      <c r="G47">
-        <v>0.7831359031025733</v>
-      </c>
-      <c r="H47">
-        <v>0.8039698677329381</v>
-      </c>
-      <c r="I47">
-        <v>0.8309401609815138</v>
-      </c>
-      <c r="J47">
-        <v>0.8556973560851393</v>
-      </c>
-      <c r="K47">
-        <v>0.8870886374647785</v>
-      </c>
-      <c r="L47">
-        <v>0.9116029094920303</v>
-      </c>
-      <c r="M47">
-        <v>0.926328412427</v>
-      </c>
-      <c r="N47">
-        <v>0.9323724169282548</v>
-      </c>
-      <c r="O47">
         <v>0.9403440074966081</v>
       </c>
-      <c r="P47">
+      <c r="Q43">
         <v>0.948627670493715</v>
       </c>
     </row>
